--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/6825-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/6825-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B9926A9-1EB1-46CD-9266-7BB185926D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93644285-B2BD-4D2B-AF60-F1B26B1432E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{33E2F6E7-9439-4A41-A3CF-E6129E860B34}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{C8888D0A-1197-446B-A35B-B63C2F7B3A7A}"/>
   </bookViews>
   <sheets>
     <sheet name="6825-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1250,21 +1250,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0401A6A-96AD-404C-9216-68464E392BB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D5B145E-B155-4C05-B48E-DE914A3A92CB}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" customWidth="1"/>
+    <col min="1" max="4" width="8.6328125" customWidth="1"/>
+    <col min="5" max="6" width="9.08984375" customWidth="1"/>
+    <col min="7" max="9" width="8.6328125" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1295,7 @@
       <c r="P1" s="17"/>
       <c r="Q1" s="18"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="14"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1346,7 +1346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="15"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1383,7 +1383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
         <v>20</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
